--- a/artfynd/A 11851-2024 artfynd.xlsx
+++ b/artfynd/A 11851-2024 artfynd.xlsx
@@ -1605,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117736610</v>
+        <v>117751062</v>
       </c>
       <c r="B11" t="n">
-        <v>90446</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,37 +1621,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>822877</v>
+        <v>822839</v>
       </c>
       <c r="R11" t="n">
-        <v>7289942</v>
+        <v>7290055</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,12 +1675,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,7 +1689,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117751062</v>
+        <v>117736610</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>90446</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,34 +1723,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>822839</v>
+        <v>822877</v>
       </c>
       <c r="R12" t="n">
-        <v>7290055</v>
+        <v>7289942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,12 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,6 +1794,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11851-2024 artfynd.xlsx
+++ b/artfynd/A 11851-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117736603</v>
+        <v>117736607</v>
       </c>
       <c r="B2" t="n">
         <v>90517</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>823051</v>
+        <v>822958</v>
       </c>
       <c r="R2" t="n">
-        <v>7289693</v>
+        <v>7289906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117736617</v>
+        <v>117736603</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>822823</v>
+        <v>823051</v>
       </c>
       <c r="R3" t="n">
-        <v>7289804</v>
+        <v>7289693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117736616</v>
+        <v>117736614</v>
       </c>
       <c r="B4" t="n">
         <v>78480</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>822831</v>
+        <v>823064</v>
       </c>
       <c r="R4" t="n">
-        <v>7289805</v>
+        <v>7289685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117736614</v>
+        <v>117736597</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>57308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>823064</v>
+        <v>822804</v>
       </c>
       <c r="R6" t="n">
-        <v>7289685</v>
+        <v>7289813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117736597</v>
+        <v>117736616</v>
       </c>
       <c r="B7" t="n">
-        <v>57308</v>
+        <v>78480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,50 +1209,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>822804</v>
+        <v>822831</v>
       </c>
       <c r="R7" t="n">
-        <v>7289813</v>
+        <v>7289805</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117736607</v>
+        <v>117736617</v>
       </c>
       <c r="B8" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>822958</v>
+        <v>822823</v>
       </c>
       <c r="R8" t="n">
-        <v>7289906</v>
+        <v>7289804</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117751058</v>
+        <v>117751059</v>
       </c>
       <c r="B9" t="n">
         <v>78480</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>822838</v>
+        <v>822894</v>
       </c>
       <c r="R9" t="n">
-        <v>7290009</v>
+        <v>7289857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117751062</v>
+        <v>117751052</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,34 +1621,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>822839</v>
+        <v>822957</v>
       </c>
       <c r="R11" t="n">
-        <v>7290055</v>
+        <v>7289774</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1692,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117751061</v>
+        <v>117751058</v>
       </c>
       <c r="B13" t="n">
         <v>78480</v>
@@ -1853,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>822877</v>
+        <v>822838</v>
       </c>
       <c r="R13" t="n">
-        <v>7289942</v>
+        <v>7290009</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117751052</v>
+        <v>117751061</v>
       </c>
       <c r="B14" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,37 +1935,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>822957</v>
+        <v>822877</v>
       </c>
       <c r="R14" t="n">
-        <v>7289774</v>
+        <v>7289942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,7 +2003,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117751059</v>
+        <v>117751062</v>
       </c>
       <c r="B15" t="n">
         <v>78480</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>822894</v>
+        <v>822839</v>
       </c>
       <c r="R15" t="n">
-        <v>7289857</v>
+        <v>7290055</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 11851-2024 artfynd.xlsx
+++ b/artfynd/A 11851-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117736607</v>
+        <v>117736617</v>
       </c>
       <c r="B2" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>822958</v>
+        <v>822823</v>
       </c>
       <c r="R2" t="n">
-        <v>7289906</v>
+        <v>7289804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117736603</v>
+        <v>117736616</v>
       </c>
       <c r="B3" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>823051</v>
+        <v>822831</v>
       </c>
       <c r="R3" t="n">
-        <v>7289693</v>
+        <v>7289805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117736614</v>
+        <v>117736607</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>823064</v>
+        <v>822958</v>
       </c>
       <c r="R4" t="n">
-        <v>7289685</v>
+        <v>7289906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117736615</v>
+        <v>117736597</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>57309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>822919</v>
+        <v>822804</v>
       </c>
       <c r="R5" t="n">
-        <v>7289765</v>
+        <v>7289813</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117736597</v>
+        <v>117736603</v>
       </c>
       <c r="B6" t="n">
-        <v>57308</v>
+        <v>90519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,50 +1107,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100110</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>822804</v>
+        <v>823051</v>
       </c>
       <c r="R6" t="n">
-        <v>7289813</v>
+        <v>7289693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117736616</v>
+        <v>117736614</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>822831</v>
+        <v>823064</v>
       </c>
       <c r="R7" t="n">
-        <v>7289805</v>
+        <v>7289685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117736617</v>
+        <v>117736615</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>822823</v>
+        <v>822919</v>
       </c>
       <c r="R8" t="n">
-        <v>7289804</v>
+        <v>7289765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117751059</v>
+        <v>117751061</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>822894</v>
+        <v>822877</v>
       </c>
       <c r="R9" t="n">
-        <v>7289857</v>
+        <v>7289942</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117751057</v>
+        <v>117751059</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>822787</v>
+        <v>822894</v>
       </c>
       <c r="R10" t="n">
-        <v>7290047</v>
+        <v>7289857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117751052</v>
+        <v>117751058</v>
       </c>
       <c r="B11" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,37 +1621,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>822957</v>
+        <v>822838</v>
       </c>
       <c r="R11" t="n">
-        <v>7289774</v>
+        <v>7290009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1689,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117736610</v>
+        <v>117751062</v>
       </c>
       <c r="B12" t="n">
-        <v>90446</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,37 +1723,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>822877</v>
+        <v>822839</v>
       </c>
       <c r="R12" t="n">
-        <v>7289942</v>
+        <v>7290055</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1777,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,7 +1791,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117751058</v>
+        <v>117751052</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>90519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,34 +1825,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>822838</v>
+        <v>822957</v>
       </c>
       <c r="R13" t="n">
-        <v>7290009</v>
+        <v>7289774</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117751061</v>
+        <v>117751057</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>822877</v>
+        <v>822787</v>
       </c>
       <c r="R14" t="n">
-        <v>7289942</v>
+        <v>7290047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117751062</v>
+        <v>117736610</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>90448</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,34 +2033,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>822839</v>
+        <v>822877</v>
       </c>
       <c r="R15" t="n">
-        <v>7290055</v>
+        <v>7289942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,12 +2090,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2105,6 +2104,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11851-2024 artfynd.xlsx
+++ b/artfynd/A 11851-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117736607</v>
+        <v>117736597</v>
       </c>
       <c r="B4" t="n">
-        <v>90519</v>
+        <v>57309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>822958</v>
+        <v>822804</v>
       </c>
       <c r="R4" t="n">
-        <v>7289906</v>
+        <v>7289813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117736597</v>
+        <v>117736607</v>
       </c>
       <c r="B5" t="n">
-        <v>57309</v>
+        <v>90519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100110</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>822804</v>
+        <v>822958</v>
       </c>
       <c r="R5" t="n">
-        <v>7289813</v>
+        <v>7289906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11851-2024 artfynd.xlsx
+++ b/artfynd/A 11851-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117736603</v>
+        <v>117736610</v>
       </c>
       <c r="B2" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>823051</v>
+        <v>822877</v>
       </c>
       <c r="R2" t="n">
-        <v>7289693</v>
+        <v>7289942</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,19 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117736615</v>
+        <v>117736613</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>822919</v>
+        <v>823072</v>
       </c>
       <c r="R3" t="n">
-        <v>7289765</v>
+        <v>7289667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117736607</v>
+        <v>117736614</v>
       </c>
       <c r="B4" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>822958</v>
+        <v>823064</v>
       </c>
       <c r="R4" t="n">
-        <v>7289906</v>
+        <v>7289685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +970,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117736614</v>
+        <v>117736615</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>823064</v>
+        <v>822919</v>
       </c>
       <c r="R5" t="n">
-        <v>7289685</v>
+        <v>7289765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,62 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117736597</v>
+        <v>117736616</v>
       </c>
       <c r="B6" t="n">
-        <v>57311</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>822804</v>
+        <v>822831</v>
       </c>
       <c r="R6" t="n">
-        <v>7289813</v>
+        <v>7289805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,19 +1164,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117736616</v>
+        <v>117736617</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1237,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>822831</v>
+        <v>822823</v>
       </c>
       <c r="R7" t="n">
-        <v>7289805</v>
+        <v>7289804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,19 +1261,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117736617</v>
+        <v>117751057</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1339,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>822823</v>
+        <v>822787</v>
       </c>
       <c r="R8" t="n">
-        <v>7289804</v>
+        <v>7290047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,12 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,19 +1358,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117751059</v>
+        <v>117751058</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1441,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>822894</v>
+        <v>822838</v>
       </c>
       <c r="R9" t="n">
-        <v>7289857</v>
+        <v>7290009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,53 +1455,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117736610</v>
+        <v>117751059</v>
       </c>
       <c r="B10" t="n">
-        <v>90450</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>822877</v>
+        <v>822894</v>
       </c>
       <c r="R10" t="n">
-        <v>7289942</v>
+        <v>7289857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1534,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1609,19 +1552,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117751057</v>
+        <v>117751060</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1649,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>822787</v>
+        <v>823068</v>
       </c>
       <c r="R11" t="n">
-        <v>7290047</v>
+        <v>7289669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,16 +1652,11 @@
         <v>117751061</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1813,53 +1746,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117751052</v>
+        <v>117751062</v>
       </c>
       <c r="B13" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>822957</v>
+        <v>822839</v>
       </c>
       <c r="R13" t="n">
-        <v>7289774</v>
+        <v>7290055</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1825,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,50 +1843,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117751058</v>
+        <v>117736597</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddviksheden syd, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>822838</v>
+        <v>822804</v>
       </c>
       <c r="R14" t="n">
-        <v>7290009</v>
+        <v>7289813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,12 +1920,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2018,108 +1949,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>117751062</v>
-      </c>
-      <c r="B15" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Gäddviksheden syd, Nb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>822839</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7290055</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Nederluleå</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11851-2024 artfynd.xlsx
+++ b/artfynd/A 11851-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736610</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736615</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736616</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736617</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117751057</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117751058</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117751059</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117751060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117751061</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117751062</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,8 +2014,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117736597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>